--- a/medicines.xlsx
+++ b/medicines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shimi\OneDrive\デスクトップ\otc_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C4B5746-A044-437A-BF54-372BA289CAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{464D61E1-4A0F-4BD8-B73B-15407C68F7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="696" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="シート1" sheetId="1" r:id="rId1"/>
